--- a/Gstsaralprotesting/src/test/java/pro/saral/testData/Deductor_Details.xlsx
+++ b/Gstsaralprotesting/src/test/java/pro/saral/testData/Deductor_Details.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujatha\git\Gstsaralprotesting\Gstsaralprotesting\src\test\java\pro\saral\testData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900F9BCB-A371-4F94-9EE3-984ED00F322D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Deductor" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -195,9 +189,6 @@
     <t>Kerala</t>
   </si>
   <si>
-    <t>TDS</t>
-  </si>
-  <si>
     <t>Saral_TDS</t>
   </si>
   <si>
@@ -282,14 +273,17 @@
     <t>TDS_Import</t>
   </si>
   <si>
-    <t>Saral_Pro_D</t>
+    <t>Saral_Pro_E</t>
+  </si>
+  <si>
+    <t>TDS1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,7 +463,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -504,7 +498,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -681,16 +675,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
@@ -705,7 +699,7 @@
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
         <v>35</v>
       </c>
@@ -732,9 +726,9 @@
       </c>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>85</v>
+    <row r="2" spans="1:10" s="5" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -758,14 +752,14 @@
         <v>8976582536</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="5" customFormat="1"/>
+    <row r="4" spans="1:10" s="11" customFormat="1"/>
+    <row r="5" spans="1:10" s="11" customFormat="1"/>
+    <row r="6" spans="1:10" s="11" customFormat="1"/>
+    <row r="7" spans="1:10" s="11" customFormat="1"/>
+    <row r="8" spans="1:10" s="5" customFormat="1"/>
+    <row r="9" spans="1:10" s="5" customFormat="1"/>
+    <row r="10" spans="1:10" s="5" customFormat="1">
       <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
@@ -797,7 +791,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="5" customFormat="1">
       <c r="A11" s="11" t="s">
         <v>53</v>
       </c>
@@ -817,24 +811,24 @@
         <v>8736458356</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="5" customFormat="1">
       <c r="A12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>43</v>
@@ -843,69 +837,69 @@
         <v>23</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" s="11">
         <v>8757656565</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="4" customFormat="1">
       <c r="A13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>65</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="11">
         <v>7558656565</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="11" customFormat="1">
       <c r="A14" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="14"/>
       <c r="F14" s="12"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="11" customFormat="1">
       <c r="C15" s="14"/>
       <c r="F15" s="12"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" s="11" customFormat="1">
       <c r="C16" s="14"/>
       <c r="F16" s="12"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" s="11" customFormat="1">
       <c r="C17" s="14"/>
       <c r="F17" s="12"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" s="11" customFormat="1">
       <c r="C18" s="14"/>
       <c r="F18" s="12"/>
       <c r="I18" s="13"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -916,7 +910,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18">
       <c r="A20" s="6" t="s">
         <v>0</v>
       </c>
@@ -972,9 +966,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>17</v>
@@ -1016,8 +1010,8 @@
         <v>9000000000</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:18" ht="33" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="11" customFormat="1"/>
+    <row r="30" spans="1:18" ht="30">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1096,10 +1090,10 @@
         <v>9000000000</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="C34" s="9"/>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="15" t="s">
         <v>4</v>
       </c>
@@ -1107,33 +1101,33 @@
         <v>3</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>51</v>
       </c>
       <c r="G40" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="I40" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="I40" s="15" t="s">
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>74</v>
-      </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C41" s="16">
         <v>43891</v>
@@ -1151,47 +1145,47 @@
         <v>44621</v>
       </c>
       <c r="H41" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I41" s="12" t="s">
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
       <c r="H42" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="11"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="B44" t="s">
         <v>80</v>
       </c>
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N31" r:id="rId1" xr:uid="{401CADAB-70F7-4E57-84E2-43665F77E717}"/>
-    <hyperlink ref="F12" r:id="rId2" xr:uid="{475E3D09-F9D1-4612-A7FE-6FA45A288C1C}"/>
-    <hyperlink ref="I41" r:id="rId3" xr:uid="{FE3E2C81-1FB2-406E-B898-A18BF877D8D3}"/>
+    <hyperlink ref="N31" r:id="rId1"/>
+    <hyperlink ref="F12" r:id="rId2"/>
+    <hyperlink ref="I41" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
